--- a/data/credit_bond_all_2026-09-11.xlsx
+++ b/data/credit_bond_all_2026-09-11.xlsx
@@ -1165,8 +1165,12 @@
           <t>1.40 ~ 2.00</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>15.74</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.80</t>
@@ -1399,8 +1403,12 @@
           <t>1.41 ~ 1.61</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>19.54</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>1.46</t>
@@ -1627,8 +1635,12 @@
           <t>1.33 ~ 1.73</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>22.25</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -1857,8 +1869,12 @@
           <t>1.27 ~ 1.47</t>
         </is>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="H8" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>16.3</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>1.47</t>
@@ -1915,7 +1931,7 @@
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.2</v>
+        <v>1.145</v>
       </c>
       <c r="V8" s="4" t="n">
         <v>1.15</v>
@@ -2087,8 +2103,12 @@
           <t>1.30 ~ 2.20</t>
         </is>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>22.74</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>1.70</t>
@@ -2315,8 +2335,12 @@
           <t>1.27 ~ 1.47</t>
         </is>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="H10" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>16.3</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>1.47</t>
@@ -2779,8 +2803,12 @@
           <t>1.25 ~ 1.65</t>
         </is>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+      <c r="H12" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>20.72</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>1.46</t>
@@ -3009,8 +3037,12 @@
           <t>1.27 ~ 1.47</t>
         </is>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="H13" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>16.3</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>1.47</t>
@@ -3241,8 +3273,12 @@
           <t>1.80 ~ 2.04</t>
         </is>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="H14" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>46.64</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>2.02</t>
@@ -3298,7 +3334,9 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U14" s="3"/>
+      <c r="U14" s="4" t="n">
+        <v>1.75</v>
+      </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
@@ -3697,8 +3735,12 @@
           <t>1.60 ~ 2.60</t>
         </is>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="H16" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>47.74</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>1.91</t>
@@ -3933,8 +3975,12 @@
           <t>1.50 ~ 1.90</t>
         </is>
       </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="H17" s="4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>45.96</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>1.72</t>
@@ -5071,8 +5117,12 @@
           <t>1.30 ~ 1.70</t>
         </is>
       </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="H22" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>14.46</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>1.50</t>
@@ -5584,7 +5634,9 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U24" s="3"/>
+      <c r="U24" s="4" t="n">
+        <v>3.46</v>
+      </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -5816,7 +5868,9 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U25" s="3"/>
+      <c r="U25" s="4" t="n">
+        <v>3.43</v>
+      </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
@@ -6044,7 +6098,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U26" s="3"/>
+      <c r="U26" s="4" t="n">
+        <v>2.99</v>
+      </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
@@ -6683,7 +6739,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -6715,7 +6771,11 @@
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>1.80%~1.90%</t>
+        </is>
+      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6873,8 +6933,12 @@
           <t>1.35 ~ 1.65</t>
         </is>
       </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+      <c r="H30" s="4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>21.72</v>
+      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
           <t>1.46</t>
@@ -7335,8 +7399,12 @@
           <t>1.30 ~ 1.57</t>
         </is>
       </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="H32" s="4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>25.54</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
           <t>1.57</t>
@@ -7569,8 +7637,12 @@
           <t>1.60 ~ 2.20</t>
         </is>
       </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="H33" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>54.96</v>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
           <t>1.84</t>
@@ -8225,8 +8297,12 @@
           <t>1.70 ~ 2.30</t>
         </is>
       </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+      <c r="H36" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>45.74</v>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
           <t>1.88</t>
@@ -8461,8 +8537,12 @@
           <t>1.20 ~ 2.00</t>
         </is>
       </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+      <c r="H37" s="4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>20.34</v>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
           <t>1.57</t>
@@ -8978,7 +9058,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U39" s="3"/>
+      <c r="U39" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3" t="inlineStr">
@@ -9377,8 +9459,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+      <c r="H41" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>27.74</v>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
           <t>1.76</t>
@@ -10806,7 +10892,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U47" s="3"/>
+      <c r="U47" s="4" t="n">
+        <v>3.54</v>
+      </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
@@ -11034,7 +11122,9 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U48" s="3"/>
+      <c r="U48" s="4" t="n">
+        <v>2.77</v>
+      </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
@@ -11710,7 +11800,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U51" s="3"/>
+      <c r="U51" s="4" t="n">
+        <v>3.58</v>
+      </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="inlineStr">
         <is>
@@ -11938,7 +12030,9 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U52" s="3"/>
+      <c r="U52" s="4" t="n">
+        <v>5.14</v>
+      </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>
@@ -12858,7 +12952,9 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U56" s="3"/>
+      <c r="U56" s="4" t="n">
+        <v>5.7</v>
+      </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_all_2026-09-11.xlsx
+++ b/data/credit_bond_all_2026-09-11.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-16" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-17" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-16</t>
+          <t>数据来源：DM    2026-09-17</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.74</t>
+          <t>C+ 30.75</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -1136,7 +1136,7 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26华能水电SCP011</t>
+          <t>26中交疏浚SCP002</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1146,64 +1146,64 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>012682241.IB</t>
+          <t>012682240.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0.47Y</t>
+          <t>0.73Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.41 ~ 1.61</t>
+          <t>1.33 ~ 1.73</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>19.54</v>
+        <v>22.25</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26华能水电GN011(乡村振兴)</t>
+          <t>24疏浚K1</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>181D</t>
+          <t>195D</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.5083</t>
+          <t>1.5035</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1.5300/--</t>
+          <t>--/1.4900</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>华能澜沧江水电股份有限公司</t>
+          <t>中交疏浚(集团)股份有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 22.23</t>
+          <t>B- 37.50</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="U5" s="4" t="n">
-        <v>3.92</v>
+        <v>2.14</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>1.41</v>
+        <v>1.0</v>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1250,17 +1250,17 @@
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>云南省-昆明市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券募集资金15亿元,募集资金拟用于偿还金融机构借款</t>
+          <t>本期发行超短期融资券5亿元,全部用于偿还发行人到期有息债务。</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>华能澜沧江水电股份有限公司2026年度第十一期超短期融资券</t>
+          <t>中交疏浚(集团)股份有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2027-06-08</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
@@ -1317,27 +1317,27 @@
       </c>
       <c r="AP5" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ5" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>其他专业工程</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26中交疏浚SCP002</t>
+          <t>26深圳国际MTN005</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1380,64 +1380,64 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>012682240.IB</t>
+          <t>102683609.IB</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>0.73Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.33 ~ 1.73</t>
+          <t>1.30 ~ 2.20</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>22.25</v>
+        <v>22.74</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>24疏浚K1</t>
+          <t>26深圳国控MTN003</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>195D</t>
+          <t>4.85Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.5035</t>
+          <t>1.7442</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/1.4900</t>
+          <t>1.7600/1.7450</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>中交疏浚(集团)股份有限公司</t>
+          <t>深圳国际控股有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>B- 41.00</t>
+          <t>C 27.54</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>09-11 09:00</t>
+          <t>09-11 10:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
@@ -1461,19 +1461,15 @@
         </is>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.14</v>
+        <v>3.19</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+        <v>11.25</v>
+      </c>
+      <c r="W6" s="3"/>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1482,30 +1478,26 @@
         </is>
       </c>
       <c r="Z6" s="3"/>
-      <c r="AA6" s="3" t="inlineStr">
-        <is>
-          <t>上海市</t>
-        </is>
-      </c>
+      <c r="AA6" s="3"/>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期发行超短期融资券5亿元,全部用于偿还发行人到期有息债务。</t>
+          <t>本期中期票据发行规模为人民币10亿元，拟使用9.56亿元用于偿还有息债务本息，约0.44亿元用于下属子公司深国际控股(深圳)有限公司补充流动资金。[23 国际P7]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,平安银行股份有限公司</t>
+          <t>兴业银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG6" s="3" t="inlineStr">
@@ -1515,7 +1507,7 @@
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>中交疏浚(集团)股份有限公司2026年度第二期超短期融资券</t>
+          <t>深圳国际控股有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
@@ -1525,10 +1517,14 @@
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2027-06-08</t>
-        </is>
-      </c>
-      <c r="AK6" s="3"/>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL6" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -1551,27 +1547,27 @@
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>其他专业工程</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1599,12 +1595,14 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ6" s="3"/>
+      <c r="AZ6" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26深圳国际MTN005</t>
+          <t>26乐山国资MTN004</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1614,7 +1612,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>102683609.IB</t>
+          <t>102690030.IB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1623,55 +1621,55 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.20</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>22.74</v>
+        <v>47.74</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26深圳国控MTN003</t>
+          <t>26乐山国资MTN003</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>4.85Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.7442</t>
+          <t>1.9014</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.7450</t>
+          <t>1.9100/1.8900</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>深圳国际控股有限公司</t>
+          <t>乐山国有资产投资运营(集团)有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.51</t>
+          <t>B- 41.84</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1681,7 +1679,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>09-11 10:00</t>
+          <t>09-11 14:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1695,32 +1693,40 @@
         </is>
       </c>
       <c r="U7" s="4" t="n">
-        <v>3.19</v>
+        <v>4.44</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="W7" s="3"/>
+        <v>1.27</v>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>四川省-乐山市</t>
+        </is>
+      </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模为人民币10亿元，拟使用9.56亿元用于偿还有息债务本息，约0.44亿元用于下属子公司深国际控股(深圳)有限公司补充流动资金。[23 国际P7]</t>
+          <t>发行人本期中期票据采用发行金额动态调整机制,基础发行金额0亿元,发行金额上限5亿元,拟用于偿还发行人本部及子公司到期债务。[23乐山国资PPN002]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>中信证券股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
@@ -1741,7 +1747,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>深圳国际控股有限公司2026年度第五期中期票据</t>
+          <t>乐山国有资产投资运营(集团)有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1776,32 +1782,32 @@
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1836,7 +1842,7 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26乐山国资MTN004</t>
+          <t>26吴中城投MTN003</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1846,64 +1852,64 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>102690030.IB</t>
+          <t>102683608.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>47.74</v>
+        <v>45.96</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26乐山国资MTN003</t>
+          <t>26吴中城投MTN001</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.9014</t>
+          <t>1.7159</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.9100/1.8900</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>乐山国有资产投资运营(集团)有限公司</t>
+          <t>苏州市吴中城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>B- 42.27</t>
+          <t>C- 17.58</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1913,7 +1919,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>09-11 14:00</t>
+          <t>09-11 09:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -1927,19 +1933,19 @@
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>4.44</v>
+        <v>3.3</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>1.27</v>
+        <v>3.0</v>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1950,17 +1956,17 @@
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>四川省-乐山市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据采用发行金额动态调整机制,基础发行金额0亿元,发行金额上限5亿元,拟用于偿还发行人本部及子公司到期债务。[23乐山国资PPN002]</t>
+          <t>发行人本期债务融资工具发行金额1.00亿元,拟全部用于归还发行人即将到期的债务融资工具本金。[26吴中城投SCP001]</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信银行股份有限公司</t>
+          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
@@ -1981,7 +1987,7 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>乐山国有资产投资运营(集团)有限公司2026年度第四期中期票据</t>
+          <t>苏州市吴中城市建设投资集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1991,14 +1997,10 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK8" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-14</t>
+        </is>
+      </c>
+      <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -2016,34 +2018,34 @@
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR8" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
       <c r="AU8" s="3" t="inlineStr">
         <is>
           <t/>
@@ -2070,80 +2072,76 @@
         </is>
       </c>
       <c r="AZ8" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26吴中城投MTN003</t>
+          <t>26财通证券CP003</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
+          <t>09-11 17:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>102683608.IB</t>
+          <t>072610181.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.68Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.0</v>
+        <v>20.0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 1.90</t>
-        </is>
-      </c>
+        <v>20.0</v>
+      </c>
+      <c r="G9" s="3"/>
       <c r="H9" s="4" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>45.96</v>
+        <v>30.25</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26吴中城投MTN001</t>
+          <t>26财通证券CP002</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>182D</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.7159</t>
+          <t>1.4953</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>--/1.4800</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>苏州市吴中城市建设投资集团有限公司</t>
+          <t>财通证券股份有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 16.75</t>
+          <t>B- 37.41</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2166,47 +2164,39 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U9" s="4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V9" s="4" t="n">
-        <v>3.0</v>
-      </c>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="inlineStr">
-        <is>
-          <t>发行人本期债务融资工具发行金额1.00亿元,拟全部用于归还发行人即将到期的债务融资工具本金。[26吴中城投SCP001]</t>
-        </is>
-      </c>
+          <t>浙江省-杭州市</t>
+        </is>
+      </c>
+      <c r="AB9" s="3"/>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中信银行股份有限公司</t>
+          <t>财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2221,7 +2211,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>苏州市吴中城市建设投资集团有限公司2026年度第三期中期票据</t>
+          <t>财通证券股份有限公司2026年度第三期短期融资券</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2231,7 +2221,7 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t>2027-05-21</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
@@ -2242,7 +2232,7 @@
       </c>
       <c r="AM9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AN9" s="3" t="inlineStr">
@@ -2252,32 +2242,32 @@
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2305,77 +2295,79 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ9" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ9" s="3"/>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26财通证券CP003</t>
+          <t>26北京一轻SCP003</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>09-11 17:00</t>
+          <t>09-11 18:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>072610181.IB</t>
+          <t>012682239.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.68Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="G10" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 1.70</t>
+        </is>
+      </c>
       <c r="H10" s="4" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>30.25</v>
+        <v>14.46</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26财通证券CP002</t>
+          <t>26北京一轻MTN001</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>182D</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.4953</t>
+          <t>1.6936</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/1.4800</t>
+          <t>--/1.6097</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司</t>
+          <t>北京一轻控股有限责任公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>B- 39.39</t>
+          <t>C- 17.14</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2398,16 +2390,20 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+      <c r="U10" s="4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.46%~1.50%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -2418,19 +2414,23 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
-        </is>
-      </c>
-      <c r="AB10" s="3"/>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>本期超短期融资券发行金额10亿元,拟全部用于偿还发行人本部到期债券北京一轻控股有限责任公司2026年度第二期超短期融资券。[26北京一轻SCP002]</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司</t>
+          <t>北京银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司2026年度第三期短期融资券</t>
+          <t>北京一轻控股有限责任公司2026年度第三期超短期融资券</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2027-05-21</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
@@ -2466,17 +2466,17 @@
       </c>
       <c r="AM10" s="3" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>轻工制造</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>综合轻工制造</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>综合轻工制造</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>饮料制造</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2534,74 +2534,74 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26北京一轻SCP003</t>
+          <t>26华电K6</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
+          <t>09-11 19:00</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>012682239.IB</t>
+          <t>246055.SH</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.70</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>14.46</v>
+        <v>35.96</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26北京一轻MTN001</t>
+          <t>26华电K5</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.6936</t>
+          <t>1.6111</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/1.6097</t>
+          <t>1.6200/1.6150</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>北京一轻控股有限责任公司</t>
+          <t>中国华电集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>B- 40.38</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-11 09:00</t>
+          <t>09-11 16:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2625,19 +2625,17 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>1.2</v>
-      </c>
+        <v>3.43</v>
+      </c>
+      <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.46%~1.50%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -2648,38 +2646,38 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>河北省-保定市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额10亿元,拟全部用于偿还发行人本部到期债券北京一轻控股有限责任公司2026年度第二期超短期融资券。[26北京一轻SCP002]</t>
+          <t>本期债券发行规模为不超过20亿元,募集资金拟用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,招商证券股份有限公司,平安证券股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>北京一轻控股有限责任公司2026年度第三期超短期融资券</t>
+          <t>中国华电集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2689,13 +2687,13 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM11" s="3" t="inlineStr">
@@ -2715,27 +2713,27 @@
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>轻工制造</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>综合轻工制造</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>综合轻工制造</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>饮料制造</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2768,74 +2766,74 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26华电K6</t>
+          <t>26张家城投MTN005</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>09-11 19:00</t>
+          <t>09-11 18:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>246055.SH</t>
+          <t>102683614.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.80 ~ 2.04</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.61</v>
+        <v>2.0</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>35.96</v>
+        <v>46.64</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26华电K5</t>
+          <t>26张家城投MTN004</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>6.82Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.6111</t>
+          <t>2.0460</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>1.6200/1.6150</t>
+          <t>2.0500/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>中国华电集团有限公司</t>
+          <t>张家港市城市投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 40.75</t>
+          <t>C- 19.46</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2845,7 +2843,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>09-11 16:00</t>
+          <t>09-11 09:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2859,59 +2857,59 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>3.43</v>
+        <v>1.75</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.96%~2.06%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>河北省-保定市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过20亿元,募集资金拟用于生产性支出,包括偿还有息债务、补充流动资金、项目投资及运营等符合法律法规要求的用途。</t>
+          <t>本期发行金额4亿元,拟全部用于偿还本部债务融资工具本金。[21张家城投MTN004]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,招商证券股份有限公司,平安证券股份有限公司,光大证券股份有限公司</t>
+          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>中国华电集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第五期)</t>
+          <t>张家港市城市投资发展集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2921,13 +2919,13 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t>2033-09-14</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM12" s="3" t="inlineStr">
@@ -2942,32 +2940,32 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -3000,74 +2998,74 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26张家城投MTN005</t>
+          <t>26兵器K1</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
+          <t>09-11 19:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>102683614.IB</t>
+          <t>246073.SH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.04</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.0</v>
+        <v>1.64</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>46.64</v>
+        <v>21.74</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26张家城投MTN004</t>
+          <t>26兵器MTN003(科创债)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>6.82Y</t>
+          <t>4.75Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>2.0460</t>
+          <t>1.7147</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>2.0500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>张家港市城市投资发展集团有限公司</t>
+          <t>中国兵器工业集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C- 19.83</t>
+          <t>B- 47.59</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3077,7 +3075,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-11 09:00</t>
+          <t>09-11 16:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3091,59 +3089,59 @@
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.75</v>
+        <v>3.455</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.96%~2.06%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额4亿元,拟全部用于偿还本部债务融资工具本金。[21张家城投MTN004]</t>
+          <t>本期债券募集资金扣除发行费用后拟用于生产性支出,包括偿还公司债务、补充流动资金、项目建设及运营、科技创新领域相关投资支出等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>张家港市城市投资发展集团有限公司2026年度第五期中期票据</t>
+          <t>中国兵器工业集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3153,18 +3151,22 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2033-09-14</t>
-        </is>
-      </c>
-      <c r="AK13" s="3"/>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN13" s="3" t="inlineStr">
@@ -3174,32 +3176,32 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
+          <t>其他设备制造</t>
+        </is>
+      </c>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>军工设备</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>军工设备</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
-        </is>
-      </c>
-      <c r="AR13" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3232,7 +3234,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26兵器K1</t>
+          <t>26城资01</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3242,7 +3244,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>246073.SH</t>
+          <t>283935.SH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3251,55 +3253,55 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>21.74</v>
+        <v>97.74</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26兵器MTN003(科创债)</t>
+          <t>25城资08</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>4.75Y</t>
+          <t>4.00Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7147</t>
+          <t>2.3416</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.2500</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>中国兵器工业集团有限公司</t>
+          <t>邹城市城资控股集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 46.51</t>
+          <t>C+ 31.80</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3309,7 +3311,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-11 16:00</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3323,38 +3325,34 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>3.455</v>
+        <v>3.67</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>1.68%~1.78%</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X14" s="3"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山东省-济宁市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后拟用于生产性支出,包括偿还公司债务、补充流动资金、项目建设及运营、科技创新领域相关投资支出等符合法律法规要求的用途。</t>
+          <t>本期债券的募集资金不超过3.00亿元(含3.00亿元)，扣除发行费用后，全部用于偿还到期的公司债券本金[23城资07]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,广发证券股份有限公司,国投证券股份有限公司</t>
+          <t>德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3365,7 +3363,7 @@
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
@@ -3375,12 +3373,12 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>中国兵器工业集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>邹城市城资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
@@ -3400,7 +3398,7 @@
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
@@ -3410,32 +3408,32 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>其他设备制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>军工设备</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>军工设备</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3468,7 +3466,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26城资01</t>
+          <t>26青投02</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3478,64 +3476,64 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>283935.SH</t>
+          <t>283940.SH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>97.74</v>
+        <v>35.74</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>25城资08</t>
+          <t>26青投01</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.00Y</t>
+          <t>2.53Y+2.00Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>2.3416</t>
+          <t>1.8445</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/2.2500</t>
+          <t>1.9000/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>邹城市城资控股集团有限公司</t>
+          <t>青岛国际投资有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C 27.22</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3545,7 +3543,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-11 15:00</t>
+          <t>09-11 16:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3558,35 +3556,37 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U15" s="4" t="n">
-        <v>3.67</v>
-      </c>
+      <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X15" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>1.85%~1.95%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>山东省-济宁市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金不超过3.00亿元(含3.00亿元)，扣除发行费用后，全部用于偿还到期的公司债券本金[23城资07]</t>
+          <t>本期债券募集资金拟用于偿还发行人合并范围内有息债务</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>德邦证券股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>邹城市城资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>青岛国际投资有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AV15" s="3" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
@@ -3700,17 +3700,17 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26青投02</t>
+          <t>26栾川钼业MTN001(科创债)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>09-11 19:00</t>
+          <t>09-11 18:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>283940.SH</t>
+          <t>102683606.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -3719,55 +3719,55 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>35.74</v>
+        <v>15.74</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26青投01</t>
+          <t>25有研K1</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>2.53Y+2.00Y</t>
+          <t>3.85Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.8445</t>
+          <t>1.6798</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.9000/--</t>
+          <t>1.7150/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>青岛国际投资有限公司</t>
+          <t>洛阳栾川钼业集团股份有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>D 5.00</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>09-11 16:00</t>
+          <t>09-11 09:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3790,16 +3790,20 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>2.7333</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>1.37</v>
+      </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3810,43 +3814,43 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>河南省-洛阳市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟用于偿还发行人合并范围内有息债务</t>
+          <t>发行人本次发行15亿元中期票据募集资金计划全部用于偿还发行人有息债务</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>中国银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司,招商银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>青岛国际投资有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>洛阳栾川钼业集团股份有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
@@ -3861,7 +3865,7 @@
       </c>
       <c r="AL16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM16" s="3" t="inlineStr">
@@ -3876,32 +3880,32 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>有色</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>常用有色金属</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>稀有金属</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3934,7 +3938,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26栾川钼业MTN001(科创债)</t>
+          <t>26中铝集MTN005(科创债)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3944,64 +3948,64 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683606.IB</t>
+          <t>102683607.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>15.74</v>
+        <v>17.74</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25有研K1</t>
+          <t>26中铝集MTN003(科创债)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>3.85Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.6798</t>
+          <t>1.7467</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.7150/--</t>
+          <t>1.7500/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>洛阳栾川钼业集团股份有限公司</t>
+          <t>中国铝业集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>C+ 30.56</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4025,19 +4029,19 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.7333</v>
+        <v>3.72</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.37</v>
+        <v>1.0</v>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4048,17 +4052,17 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>河南省-洛阳市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行15亿元中期票据募集资金计划全部用于偿还发行人有息债务</t>
+          <t>发行人本期科技创新债券募集资金5亿元,用于偿还发行人本部有息债务。</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国工商银行股份有限公司,中国建设银行股份有限公司,招商银行股份有限公司,中信银行股份有限公司</t>
+          <t>江苏银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4069,7 +4073,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -4079,7 +4083,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>洛阳栾川钼业集团股份有限公司2026年度第一期科技创新债券</t>
+          <t>中国铝业集团有限公司2026年度第五期科技创新债券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4119,7 +4123,7 @@
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
@@ -4139,12 +4143,12 @@
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>稀有金属</t>
+          <t>工业金属</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t/>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
@@ -4154,7 +4158,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4172,7 +4176,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26中铝集MTN005(科创债)</t>
+          <t>26中化股SCP010</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4182,64 +4186,64 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683607.IB</t>
+          <t>012682233.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.08Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.27 ~ 1.47</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>17.74</v>
+        <v>16.3</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26中铝集MTN003(科创债)</t>
+          <t>21中化04</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>79D</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.7467</t>
+          <t>1.4992</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>中国铝业集团有限公司</t>
+          <t>中国中化股份有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C 29.73</t>
+          <t>A- 64.37</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4263,19 +4267,19 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.72</v>
+        <v>1.145</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.0</v>
+        <v>1.15</v>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.43%~1.47%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4291,23 +4295,23 @@
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>发行人本期科技创新债券募集资金5亿元,用于偿还发行人本部有息债务。</t>
+          <t>发行人本期超短期融资券的发行规模为20亿元,募集资金将用于补充流动资金及偿还有息债务。</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -4317,7 +4321,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>中国铝业集团有限公司2026年度第五期科技创新债券</t>
+          <t>中国中化股份有限公司2026年度第十期超短期融资券</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4327,14 +4331,10 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -4357,27 +4357,27 @@
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>有色</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>常用有色金属</t>
+          <t>石油化工与贸易</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>工业金属</t>
+          <t>石油开采</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4410,7 +4410,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26中化股SCP010</t>
+          <t>26江西交投MTN007</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>012682233.IB</t>
+          <t>102683615.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>0.08Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
@@ -4436,48 +4436,48 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.27 ~ 1.47</t>
+          <t>1.20 ~ 2.00</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>16.3</v>
+        <v>20.34</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>21中化04</t>
+          <t>23赣交K4</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>79D</t>
+          <t>2.01Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.4992</t>
+          <t>1.5407</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/1.4400</t>
+          <t>--/1.5200</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司</t>
+          <t>江西省交通投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>A- 63.13</t>
+          <t>B- 48.94</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4501,19 +4501,19 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.145</v>
+        <v>3.7</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>1.54%~1.64%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4524,28 +4524,28 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券的发行规模为20亿元,募集资金将用于补充流动资金及偿还有息债务。</t>
+          <t>本期债务融资工具发行金额为人民币20亿元,所募集资金拟用于偿还发行人有息债务。</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,江苏银行股份有限公司</t>
+          <t>中国民生银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司2026年度第十期超短期融资券</t>
+          <t>江西省交通投资集团有限责任公司2026年度第七期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2028-09-14</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
@@ -4586,32 +4586,32 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>石油化工与贸易</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>石油开采</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4644,7 +4644,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26江西交投MTN007</t>
+          <t>26太原钢铁SCP001</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4654,30 +4654,30 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>102683615.IB</t>
+          <t>012682232.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.49Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.00</t>
+          <t>1.30 ~ 1.57</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>20.34</v>
+        <v>25.54</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -4686,32 +4686,32 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>23赣交K4</t>
+          <t>24太原钢铁MTN001(科创票据)</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.01Y</t>
+          <t>1.15Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.5407</t>
+          <t>1.5954</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/1.5200</t>
+          <t>1.6000/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>江西省交通投资集团有限责任公司</t>
+          <t>太原钢铁(集团)有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 49.46</t>
+          <t>C- 13.00</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4735,19 +4735,19 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>3.7</v>
+        <v>4.08</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.54%~1.64%</t>
+          <t>1.61%~1.65%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4758,28 +4758,28 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>江西省</t>
+          <t>山西省-太原市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额为人民币20亿元,所募集资金拟用于偿还发行人有息债务。</t>
+          <t>发行人本期超短期融资券发行金额10亿元,用于偿还发行人有息债务及补充流动资金。</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,兴业银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>平安银行股份有限公司,中国农业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>江西省交通投资集团有限责任公司2026年度第七期中期票据</t>
+          <t>太原钢铁(集团)有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4799,10 +4799,14 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2028-09-14</t>
-        </is>
-      </c>
-      <c r="AK20" s="3"/>
+          <t>2027-03-13</t>
+        </is>
+      </c>
+      <c r="AK20" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL20" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -4820,32 +4824,32 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>其他钢铁</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4878,7 +4882,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26太原钢铁SCP001</t>
+          <t>26岭南01</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4888,64 +4892,64 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>012682232.IB</t>
+          <t>525006.SZ</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>0.49Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.57</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>25.54</v>
+        <v>30.96</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>24太原钢铁MTN001(科创票据)</t>
+          <t>26岭南商旅MTN001</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>1.15Y</t>
+          <t>2.77Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.5954</t>
+          <t>1.6854</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.6000/--</t>
+          <t>--/1.6500</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>太原钢铁(集团)有限公司</t>
+          <t>广州岭南商旅投资集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 13.00</t>
+          <t>C- 19.33</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4955,7 +4959,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>09-11 09:00</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4965,23 +4969,21 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>1.17</v>
-      </c>
+        <v>6.08</v>
+      </c>
+      <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.65%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -4992,38 +4994,38 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>山西省-太原市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券发行金额10亿元,用于偿还发行人有息债务及补充流动资金。</t>
+          <t>本期债券募集资金扣除发行费用后,将全部用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>平安银行股份有限公司,中国农业银行股份有限公司</t>
+          <t>广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>太原钢铁(集团)有限公司2026年度第一期超短期融资券</t>
+          <t>广州岭南商旅投资集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -5033,7 +5035,7 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2027-03-13</t>
+          <t>2029-09-15</t>
         </is>
       </c>
       <c r="AK21" s="3" t="inlineStr">
@@ -5043,19 +5045,19 @@
       </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -5063,27 +5065,27 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>金属和非金属矿产</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>其他零售</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>其他钢铁</t>
+          <t>其他零售</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>一般零售</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5116,17 +5118,17 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26岭南01</t>
+          <t>26云南能投GCV01</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
+          <t>09-11 19:00</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>525006.SZ</t>
+          <t>525007.SZ</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -5142,48 +5144,40 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>30.96</v>
+        <v>49.96</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>26岭南商旅MTN001</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>2.77Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.6854</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/1.6500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>广州岭南商旅投资集团有限公司</t>
+          <t>云南能源投资股份有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>D 4.33</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5207,19 +5201,15 @@
         </is>
       </c>
       <c r="U22" s="4" t="n">
-        <v>6.08</v>
+        <v>4.3</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t>1.66%~1.76%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X22" s="3"/>
       <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5228,17 +5218,17 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>云南省-昆明市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,将全部用于偿还有息债务</t>
+          <t>本期债券募集资金扣除发行费用后,拟将15,750.00万元用于偿还碳中和绿色项目有息债务;不超过34,250.00万元用于置换债券发行前12个月内对子公司的自有资金投入,穿透后专项用于绿色项目建设</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司</t>
+          <t>广发证券股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
@@ -5259,7 +5249,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>广州岭南商旅投资集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>云南能源投资股份有限公司2026年面向专业投资者公开发行碳中和绿色乡村振兴公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5284,7 +5274,7 @@
       </c>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
@@ -5297,29 +5287,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP22" s="3"/>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>其他零售</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>其他零售</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>一般零售</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5352,7 +5338,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26云南能投GCV01</t>
+          <t>26国新K3</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5362,85 +5348,93 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>525007.SZ</t>
+          <t>246086.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>49.96</v>
+        <v>23.74</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>26国新01</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>4.96Y</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>1.7307</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>1.7100/1.6800</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>中国国新控股有限责任公司</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>A- 60.28</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>09-11 16:00</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>云南能源投资股份有限公司</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>09-11 15:00</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>4.3</v>
+        <v>2.99</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X23" s="3"/>
@@ -5452,17 +5446,17 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>云南省-昆明市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将15,750.00万元用于偿还碳中和绿色项目有息债务;不超过34,250.00万元用于置换债券发行前12个月内对子公司的自有资金投入,穿透后专项用于绿色项目建设</t>
+          <t>本期债券发行金额为不超过20亿元（含），募集资金扣除发行费用后,拟全部用于偿还投资国家石油天然气 管网集团有限公司的并购贷款。</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,中信证券股份有限公司</t>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司,国新证券股份有限公司,申万宏源证券有限公司,东方证券股份有限公司,长江证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5473,17 +5467,17 @@
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>云南能源投资股份有限公司2026年面向专业投资者公开发行碳中和绿色乡村振兴公司债券(第一期)</t>
+          <t>中国国新控股有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5493,17 +5487,13 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
-        </is>
-      </c>
-      <c r="AK23" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
@@ -5521,25 +5511,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP23" s="3"/>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5572,7 +5566,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26国新K3</t>
+          <t>26乐山02</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5582,7 +5576,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>246086.SH</t>
+          <t>283993.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -5591,55 +5585,55 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.66</v>
+        <v>2.09</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>23.74</v>
+        <v>66.74</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26国新01</t>
+          <t>26乐山01</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>4.96Y</t>
+          <t>4.48Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.7307</t>
+          <t>1.8788</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.7100/1.6800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>中国国新控股有限责任公司</t>
+          <t>乐山城市更新集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.84</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5663,34 +5657,34 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>四川省-乐山市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过20亿元（含），募集资金扣除发行费用后,拟全部用于偿还投资国家石油天然气 管网集团有限公司的并购贷款。</t>
+          <t>本期债券募集资金5亿元扣除发行费用后,拟用于置换偿还到期公司债券本金的自有资金[23乐山02]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,招商证券股份有限公司,国新证券股份有限公司,申万宏源证券有限公司,东方证券股份有限公司,长江证券股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
@@ -5701,7 +5695,7 @@
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5711,12 +5705,12 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>中国国新控股有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第二期)</t>
+          <t>乐山城市更新集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
@@ -5742,32 +5736,32 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5800,7 +5794,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26乐山02</t>
+          <t>26锦汇01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5810,7 +5804,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>283993.SH</t>
+          <t>284000.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5819,40 +5813,40 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.55 ~ 2.55</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.09</v>
+        <v>2.0</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>66.74</v>
+        <v>57.74</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26乐山01</t>
+          <t>25锦汇02</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>4.48Y</t>
+          <t>3.31Y+2.00Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.8788</t>
+          <t>1.7275</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5862,12 +5856,12 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>乐山城市更新集团有限公司</t>
+          <t>江苏锦汇集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>D 3.11</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5877,7 +5871,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>09-11 16:00</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5891,7 +5885,7 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.68</v>
+        <v>2.12</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
@@ -5902,26 +5896,30 @@
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>四川省-乐山市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金5亿元扣除发行费用后,拟用于置换偿还到期公司债券本金的自有资金[23乐山02]</t>
+          <t>本期公司债券募集资金拟全部用于偿还回售或到期公司债券本金[23锦汇01]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD25" s="3"/>
+          <t>申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr">
+        <is>
+          <t>启东国有资产投资控股有限公司</t>
+        </is>
+      </c>
       <c r="AE25" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5939,7 +5937,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>乐山城市更新集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>江苏锦汇集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5955,57 +5953,57 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AO25" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ25" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR25" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW25" s="3" t="inlineStr">
@@ -6028,7 +6026,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26锦汇01</t>
+          <t>26淄博05</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6038,7 +6036,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>284000.SH</t>
+          <t>283967.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -6047,55 +6045,55 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.55 ~ 2.55</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.0</v>
+        <v>2.03</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>57.74</v>
+        <v>60.74</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>25锦汇02</t>
+          <t>26淄博04</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>3.31Y+2.00Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.7275</t>
+          <t>2.0397</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0400/2.0300</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>江苏锦汇集团有限公司</t>
+          <t>淄博市城市资产运营集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>D 3.11</t>
+          <t>B- 35.16</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6105,7 +6103,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>09-11 15:00</t>
+          <t>09-11 16:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -6119,41 +6117,41 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.12</v>
+        <v>4.18</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X26" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>1.96%~2.06%</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>山东省-淄博市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟全部用于偿还回售或到期公司债券本金[23锦汇01]</t>
+          <t>本期债券发行规模为不超过人民币5亿元(含5亿元),扣除发行费用后拟用于偿还发行人到期公司债券本金[23 淄博05]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD26" s="3" t="inlineStr">
-        <is>
-          <t>启东国有资产投资控股有限公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,长城证券股份有限公司,兴业证券股份有限公司,德邦证券股份有限公司,万联证券股份有限公司,华金证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -6171,7 +6169,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>江苏锦汇集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>淄博市城市资产运营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6187,57 +6185,57 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AO26" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ26" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR26" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW26" s="3" t="inlineStr">
@@ -6260,7 +6258,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26淄博05</t>
+          <t>26余创01</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6270,64 +6268,56 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>283967.SH</t>
+          <t>283845.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.0</v>
+        <v>18.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>60.74</v>
+        <v>53.96</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>26淄博04</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>4.92Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>2.0397</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>2.0400/2.0300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>淄博市城市资产运营集团有限公司</t>
+          <t>杭州余杭创新产业发展运营有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B- 35.48</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6337,7 +6327,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>09-11 16:00</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6351,19 +6341,15 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.18</v>
+        <v>2.9</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t>1.96%~2.06%</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X27" s="3"/>
       <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6372,17 +6358,17 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>山东省-淄博市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过人民币5亿元(含5亿元),扣除发行费用后拟用于偿还发行人到期公司债券本金[23 淄博05]</t>
+          <t>本期债券拟募集资金规模不超过18亿元(含18亿元),本期债券的募集资金扣除发行费用后,拟用于偿还有息负债等</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,长城证券股份有限公司,兴业证券股份有限公司,德邦证券股份有限公司,万联证券股份有限公司,华金证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
@@ -6403,7 +6389,7 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>淄博市城市资产运营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>杭州余杭创新产业发展运营有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6413,10 +6399,14 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
-        </is>
-      </c>
-      <c r="AK27" s="3"/>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6437,11 +6427,7 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+      <c r="AP27" s="3"/>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -6459,7 +6445,7 @@
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6492,98 +6478,112 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26余创01</t>
+          <t>26华能水电SCP011</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-11 19:00</t>
+          <t>09-11 18:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>283845.SH</t>
+          <t>012682241.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.47Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.41 ~ 1.61</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>53.96</v>
+        <v>19.54</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>26华能水电GN011(乡村振兴)</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>181D</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>1.5083</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>1.5300/--</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>华能澜沧江水电股份有限公司</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>C- 20.80</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>09-11 09:00</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>杭州余杭创新产业发展运营有限公司</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>09-11 15:00</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V28" s="3"/>
+        <v>3.92</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>1.41</v>
+      </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X28" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>1.48%~1.52%</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6592,58 +6592,54 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>云南省-昆明市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟募集资金规模不超过18亿元(含18亿元),本期债券的募集资金扣除发行费用后,拟用于偿还有息负债等</t>
+          <t>本期超短期融资券募集资金15亿元,募集资金拟用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,平安证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭创新产业发展运营有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>华能澜沧江水电股份有限公司2026年度第十一期超短期融资券</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
-        </is>
-      </c>
-      <c r="AK28" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-03-05</t>
+        </is>
+      </c>
+      <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr">
@@ -6653,7 +6649,7 @@
       </c>
       <c r="AN28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO28" s="3" t="inlineStr">
@@ -6661,25 +6657,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP28" s="3"/>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6712,17 +6712,17 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26贵州银行小微债01</t>
+          <t>26上海银行债02</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
+          <t>09-11 17:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>212680041.IB</t>
+          <t>212680040.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -6731,55 +6731,55 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>30.0</v>
+        <v>200.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>60.0</v>
+        <v>200.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>41.96</v>
+        <v>32.96</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26贵州银行债01</t>
+          <t>26上海银行债01</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>2.86Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.6734</t>
+          <t>1.5824</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>1.5850/1.5725</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>贵州银行股份有限公司</t>
+          <t>上海银行股份有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C 25.10</t>
+          <t>S- 86.76</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6802,16 +6802,14 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U29" s="3"/>
+      <c r="U29" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="V29" s="3"/>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t>5-</t>
-        </is>
-      </c>
+      <c r="W29" s="3"/>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6819,24 +6817,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z29" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集的资金将依据适用法律和主管部门的批准,全部用于向小型微型企业发放贷款。</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,东方证券股份有限公司,中国邮政储蓄银行股份有限公司,重庆银行股份有限公司,中国国际金融股份有限公司</t>
+          <t>国泰海通证券股份有限公司,国投证券股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,中国农业银行股份有限公司,中国银行股份有限公司,中国银河证券股份有限公司,中国建设银行股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6857,7 +6851,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>贵州银行股份有限公司2026年小型微型企业贷款专项金融债券(第一期)</t>
+          <t>上海银行股份有限公司2026年第二期金融债券</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6882,7 +6876,7 @@
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
@@ -6897,7 +6891,7 @@
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
@@ -6950,7 +6944,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26苏美达SCP002</t>
+          <t>26贵州银行小微债01</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6960,64 +6954,64 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>012682236.IB</t>
+          <t>212680041.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.0</v>
+        <v>60.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.65</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>21.72</v>
+        <v>41.96</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26苏美达SCP001</t>
+          <t>26贵州银行债01</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>91D</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.5000</t>
+          <t>1.6734</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/1.5000</t>
+          <t>1.6900/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>江苏苏美达集团有限公司</t>
+          <t>贵州银行股份有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C 27.50</t>
+          <t>B- 47.40</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7037,23 +7031,19 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>1.5</v>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7061,31 +7051,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z30" s="3"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>贵州省-贵阳市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额5亿元,用于偿还发行人本部及子公司有息负债。</t>
+          <t>本期债券募集的资金将依据适用法律和主管部门的批准,全部用于向小型微型企业发放贷款。</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,北京银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,东方证券股份有限公司,中国邮政储蓄银行股份有限公司,重庆银行股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
@@ -7095,7 +7089,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>江苏苏美达集团有限公司2026年度第二期超短期融资券</t>
+          <t>贵州银行股份有限公司2026年小型微型企业贷款专项金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7105,57 +7099,57 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2029-09-15</t>
         </is>
       </c>
       <c r="AK30" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AM30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7188,7 +7182,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26滨建投MTN006</t>
+          <t>26苏美达SCP002</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7198,12 +7192,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>102683612.IB</t>
+          <t>012682236.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
@@ -7214,48 +7208,48 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.35 ~ 1.65</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>54.96</v>
+        <v>21.72</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>24滨建投MTN010</t>
+          <t>26苏美达SCP001</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>91D</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.8349</t>
+          <t>1.5000</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1.8400/--</t>
+          <t>--/1.5000</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>天津滨海新区建设投资集团有限公司</t>
+          <t>江苏苏美达集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>B- 36.39</t>
+          <t>C 27.50</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7279,19 +7273,19 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4.52</v>
+        <v>1.56</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7302,28 +7296,28 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>天津市-滨海新区</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据注册规模90亿元，本期中期票据基础发行规模0亿元，发行金额上限5亿元【24滨建投MTN013】</t>
+          <t>本期超短期融资券发行金额5亿元,用于偿还发行人本部及子公司有息负债。</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -7333,7 +7327,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>天津滨海新区建设投资集团有限公司2026年度第六期中期票据</t>
+          <t>江苏苏美达集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7343,10 +7337,14 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
-        </is>
-      </c>
-      <c r="AK31" s="3"/>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="AK31" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -7364,32 +7362,32 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7417,14 +7415,12 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ31" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ31" s="3"/>
     </row>
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26湘江资产MTN001</t>
+          <t>26滨建投MTN006</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7434,64 +7430,64 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>102683611.IB</t>
+          <t>102683612.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.30</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>45.74</v>
+        <v>54.96</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>25湘江资产MTN001</t>
+          <t>24滨建投MTN010</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>1.54Y+2.00Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6250</t>
+          <t>1.8349</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>长沙湘江资产管理有限公司</t>
+          <t>天津滨海新区建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 20.91</t>
+          <t>C+ 33.38</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7515,19 +7511,19 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.52</v>
+        <v>4.52</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7538,17 +7534,17 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>天津市-滨海新区</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额为4亿元,募集资金拟全部用于偿还发行人存量有息债务。</t>
+          <t>本次中期票据注册规模90亿元，本期中期票据基础发行规模0亿元，发行金额上限5亿元【24滨建投MTN013】</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,华夏银行股份有限公司</t>
+          <t>中信银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
@@ -7569,7 +7565,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>长沙湘江资产管理有限公司2026年度第一期中期票据</t>
+          <t>天津滨海新区建设投资集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7579,14 +7575,10 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK32" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-14</t>
+        </is>
+      </c>
+      <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -7604,32 +7596,32 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7658,80 +7650,80 @@
         </is>
       </c>
       <c r="AZ32" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26上海银行债02</t>
+          <t>26湘江资产MTN001</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-11 17:00</t>
+          <t>09-11 18:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>212680040.IB</t>
+          <t>102683611.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>200.0</v>
+        <v>4.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>200.0</v>
+        <v>4.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.70 ~ 2.30</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>32.96</v>
+        <v>45.74</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26上海银行债01</t>
+          <t>25湘江资产MTN001</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.86Y</t>
+          <t>1.54Y+2.00Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.5824</t>
+          <t>1.6250</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.5850/1.5725</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司</t>
+          <t>长沙湘江资产管理有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>A 75.27</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7751,17 +7743,23 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
+        <v>3.52</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.81%~1.91%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7772,23 +7770,23 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+          <t>本期债务融资工具发行金额为4亿元,募集资金拟全部用于偿还发行人存量有息债务。</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,国投证券股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,中国农业银行股份有限公司,中国银行股份有限公司,中国银河证券股份有限公司,中国建设银行股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,兴业银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>兴业银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7803,7 +7801,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司2026年第二期金融债券</t>
+          <t>长沙湘江资产管理有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7813,17 +7811,17 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
+          <t>2031-09-14</t>
         </is>
       </c>
       <c r="AK33" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM33" s="3" t="inlineStr">
@@ -7833,7 +7831,7 @@
       </c>
       <c r="AN33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO33" s="3" t="inlineStr">
@@ -7843,27 +7841,27 @@
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>资产管理</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7891,7 +7889,9 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ33" s="3"/>
+      <c r="AZ33" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 19.60</t>
+          <t>C- 18.39</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>B 51.62</t>
+          <t>B 51.28</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.09</t>
+          <t>C 29.22</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>A- 63.13</t>
+          <t>A- 64.37</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 24.79</t>
+          <t>C 25.36</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C 29.62</t>
+          <t>C 28.38</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>A- 63.13</t>
+          <t>A- 64.37</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>A- 63.13</t>
+          <t>A- 64.37</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C- 19.83</t>
+          <t>C- 19.46</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C 29.63</t>
+          <t>C 28.87</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AL49" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM49" s="3" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>C- 15.34</t>
+          <t>C- 17.59</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -12013,7 +12013,7 @@
       <c r="AK51" s="3"/>
       <c r="AL51" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM51" s="3" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26惠州产投01</t>
+          <t>26未科06</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>520461.SZ</t>
+          <t>283912.SH</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -12105,55 +12105,55 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>27.74</v>
+        <v>31.74</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>25惠产01</t>
+          <t>26未科03</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2.21Y+2.00Y</t>
+          <t>2.59Y+2.00Y</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.6380</t>
+          <t>1.6941</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>--/1.6000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>惠州市产业投资集团有限公司</t>
+          <t>北京未来科学城发展集团有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>C- 23.93</t>
+          <t>C- 23.70</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>09-11 15:00</t>
+          <t>09-11 16:00</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -12177,38 +12177,38 @@
         </is>
       </c>
       <c r="U52" s="4" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.70%~1.80%</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>广东省-惠州市</t>
+          <t>北京市-昌平区</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还有息债务。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金或置换已用于偿还到期公司债券本金的自有资金[23未科05]</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>华金证券股份有限公司,广发证券股份有限公司</t>
+          <t>中信证券股份有限公司,光大证券股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
@@ -12224,12 +12224,12 @@
       </c>
       <c r="AG52" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>惠州市产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>北京未来科学城发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
@@ -12245,7 +12245,7 @@
       <c r="AK52" s="3"/>
       <c r="AL52" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM52" s="3" t="inlineStr">
@@ -12265,27 +12265,27 @@
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -12318,7 +12318,7 @@
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26未科06</t>
+          <t>26路科01</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>283912.SH</t>
+          <t>283958.SH</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -12337,40 +12337,40 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>31.74</v>
+        <v>37.74</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>26未科03</t>
+          <t>24靖投01</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>2.59Y+2.00Y</t>
+          <t>3.03Y</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.6941</t>
+          <t>1.7633</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -12380,12 +12380,12 @@
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>北京未来科学城发展集团有限公司</t>
+          <t>台州路桥科创集团有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>C- 21.39</t>
+          <t>D- 1.50</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12409,41 +12409,45 @@
         </is>
       </c>
       <c r="U53" s="4" t="n">
-        <v>3.58</v>
+        <v>2.09</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>1.70%~1.80%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>北京市-昌平区</t>
+          <t>浙江省-台州市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金或置换已用于偿还到期公司债券本金的自有资金[23未科05]</t>
+          <t>本期债券募集资金拟全部用于偿还到期回售的公司债券本金[23路桥01]</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,光大证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD53" s="3"/>
+          <t>中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr">
+        <is>
+          <t>台州市路桥公共资产投资管理集团有限公司</t>
+        </is>
+      </c>
       <c r="AE53" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -12461,7 +12465,7 @@
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>北京未来科学城发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>台州路桥科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -12492,12 +12496,12 @@
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP53" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ53" s="3" t="inlineStr">
@@ -12517,7 +12521,7 @@
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
@@ -12527,7 +12531,7 @@
       </c>
       <c r="AV53" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW53" s="3" t="inlineStr">
@@ -12550,7 +12554,7 @@
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26路科01</t>
+          <t>G26东田</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -12560,49 +12564,41 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>283958.SH</t>
+          <t>283915.SH</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>37.74</v>
+        <v>61.96</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr">
-        <is>
-          <t>24靖投01</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>3.03Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.7633</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -12612,12 +12608,12 @@
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>台州路桥科创集团有限公司</t>
+          <t>阜阳市东田产业投资有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>D- 1.50</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12627,7 +12623,7 @@
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>09-11 16:00</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -12641,17 +12637,13 @@
         </is>
       </c>
       <c r="U54" s="4" t="n">
-        <v>2.09</v>
+        <v>3.5267</v>
       </c>
       <c r="V54" s="3"/>
-      <c r="W54" s="3" t="inlineStr">
-        <is>
-          <t>7+</t>
-        </is>
-      </c>
+      <c r="W54" s="3"/>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>2.08%~2.18%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
@@ -12662,22 +12654,22 @@
       <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>浙江省-台州市</t>
+          <t>安徽省-阜阳市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于偿还到期回售的公司债券本金[23路桥01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将3.00亿元用于阜阳颍东区化工园区工业污水处理项目建设及运营。</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>五矿证券有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3" t="inlineStr">
         <is>
-          <t>台州市路桥公共资产投资管理集团有限公司</t>
+          <t>安徽省兴泰融资担保集团股份有限公司</t>
         </is>
       </c>
       <c r="AE54" s="3" t="inlineStr">
@@ -12697,7 +12689,7 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>台州路桥科创集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>阜阳市东田产业投资有限公司2026年面向专业投资者非公开发行绿色公司债券</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12707,60 +12699,60 @@
       </c>
       <c r="AJ54" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
-        </is>
-      </c>
-      <c r="AK54" s="3"/>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK54" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL54" s="3" t="inlineStr">
         <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP54" s="3"/>
+      <c r="AQ54" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM54" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AO54" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP54" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ54" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR54" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS54" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT54" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU54" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-15</t>
-        </is>
-      </c>
       <c r="AV54" s="3" t="inlineStr">
         <is>
           <t>有担保</t>
@@ -12768,7 +12760,7 @@
       </c>
       <c r="AW54" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX54" s="3" t="inlineStr">
@@ -12786,7 +12778,7 @@
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>G26东田</t>
+          <t>26惠州产投01</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -12796,114 +12788,122 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>283915.SH</t>
+          <t>520461.SZ</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H55" s="4" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>61.96</v>
+        <v>27.74</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>25惠产01</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>2.21Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>1.6380</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>--/1.6000</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>惠州市产业投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>C- 23.93</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>09-11 15:00</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N55" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>阜阳市东田产业投资有限公司</t>
-        </is>
-      </c>
-      <c r="P55" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="R55" s="3" t="inlineStr">
-        <is>
-          <t>09-11 15:00</t>
-        </is>
-      </c>
-      <c r="S55" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
       <c r="U55" s="4" t="n">
-        <v>3.5267</v>
+        <v>4.4</v>
       </c>
       <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>2.08%~2.18%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>安徽省-阜阳市</t>
+          <t>广东省-惠州市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将3.00亿元用于阜阳颍东区化工园区工业污水处理项目建设及运营。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司</t>
-        </is>
-      </c>
-      <c r="AD55" s="3" t="inlineStr">
-        <is>
-          <t>安徽省兴泰融资担保集团股份有限公司</t>
-        </is>
-      </c>
+          <t>华金证券股份有限公司,广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD55" s="3"/>
       <c r="AE55" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -12916,12 +12916,12 @@
       </c>
       <c r="AG55" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>阜阳市东田产业投资有限公司2026年面向专业投资者非公开发行绿色公司债券</t>
+          <t>惠州市产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
@@ -12931,68 +12931,68 @@
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK55" s="3"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
           <t>2029-09-15</t>
         </is>
       </c>
-      <c r="AK55" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
-      <c r="AL55" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AO55" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP55" s="3"/>
-      <c r="AQ55" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR55" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS55" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT55" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU55" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV55" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW55" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX55" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-11.xlsx
+++ b/data/credit_bond_all_2026-09-11.xlsx
@@ -6944,74 +6944,74 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26贵州银行小微债01</t>
+          <t>26银桥01</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
+          <t>09-11 19:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>212680041.IB</t>
+          <t>246058.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>30.0</v>
+        <v>8.9</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>60.0</v>
+        <v>8.9</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>41.96</v>
+        <v>34.74</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26贵州银行债01</t>
+          <t>26昆山银桥MTN003</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>2.37Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6734</t>
+          <t>1.6772</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>贵州银行股份有限公司</t>
+          <t>昆山银桥控股集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 47.40</t>
+          <t>C- 13.37</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>09-11 09:00</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -7034,47 +7034,41 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U30" s="3"/>
+      <c r="U30" s="4" t="n">
+        <v>6.02</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
           <t>5-</t>
         </is>
       </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t>1.66%~1.76%</t>
-        </is>
-      </c>
+      <c r="X30" s="3"/>
       <c r="Y30" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z30" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集的资金将依据适用法律和主管部门的批准,全部用于向小型微型企业发放贷款。</t>
+          <t>本期债券募集资金不超过8.90亿元(含8.90亿元),募集资金在扣除发行费用后仅用于置换偿还25银桥01公司债券本金的自有资金。[25银桥01]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,东方证券股份有限公司,中国邮政储蓄银行股份有限公司,重庆银行股份有限公司,中国国际金融股份有限公司</t>
+          <t>东吴证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -7084,12 +7078,12 @@
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>贵州银行股份有限公司2026年小型微型企业贷款专项金融债券(第一期)</t>
+          <t>昆山银桥控股集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7099,22 +7093,18 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
@@ -7124,32 +7114,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7182,7 +7172,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26苏美达SCP002</t>
+          <t>26贵州银行小微债01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7192,64 +7182,64 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>012682236.IB</t>
+          <t>212680041.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.0</v>
+        <v>60.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.65</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>21.72</v>
+        <v>41.96</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26苏美达SCP001</t>
+          <t>26贵州银行债01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>91D</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.5000</t>
+          <t>1.6734</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/1.5000</t>
+          <t>1.6900/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>江苏苏美达集团有限公司</t>
+          <t>贵州银行股份有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C 27.50</t>
+          <t>B- 47.40</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7269,23 +7259,19 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="U31" s="4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V31" s="4" t="n">
-        <v>1.5</v>
-      </c>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7293,31 +7279,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z31" s="3"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>贵州省-贵阳市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额5亿元,用于偿还发行人本部及子公司有息负债。</t>
+          <t>本期债券募集的资金将依据适用法律和主管部门的批准,全部用于向小型微型企业发放贷款。</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,北京银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,申万宏源证券有限公司,国开证券股份有限公司,东方证券股份有限公司,中国邮政储蓄银行股份有限公司,重庆银行股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -7327,7 +7317,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>江苏苏美达集团有限公司2026年度第二期超短期融资券</t>
+          <t>贵州银行股份有限公司2026年小型微型企业贷款专项金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7337,57 +7327,57 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2029-09-15</t>
         </is>
       </c>
       <c r="AK31" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AM31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7420,7 +7410,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26滨建投MTN006</t>
+          <t>26苏美达SCP002</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7430,12 +7420,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>102683612.IB</t>
+          <t>012682236.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -7446,48 +7436,48 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.35 ~ 1.65</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>54.96</v>
+        <v>21.72</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>24滨建投MTN010</t>
+          <t>26苏美达SCP001</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>91D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.8349</t>
+          <t>1.5000</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>1.8400/--</t>
+          <t>--/1.5000</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>天津滨海新区建设投资集团有限公司</t>
+          <t>江苏苏美达集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.38</t>
+          <t>C 27.50</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7511,19 +7501,19 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>4.52</v>
+        <v>1.56</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7534,28 +7524,28 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>天津市-滨海新区</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本次中期票据注册规模90亿元，本期中期票据基础发行规模0亿元，发行金额上限5亿元【24滨建投MTN013】</t>
+          <t>本期超短期融资券发行金额5亿元,用于偿还发行人本部及子公司有息负债。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7565,7 +7555,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>天津滨海新区建设投资集团有限公司2026年度第六期中期票据</t>
+          <t>江苏苏美达集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7575,10 +7565,14 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
-        </is>
-      </c>
-      <c r="AK32" s="3"/>
+          <t>2026-12-13</t>
+        </is>
+      </c>
+      <c r="AK32" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL32" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -7596,32 +7590,32 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7649,14 +7643,12 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ32" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ32" s="3"/>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26湘江资产MTN001</t>
+          <t>26滨建投MTN006</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7666,64 +7658,64 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>102683611.IB</t>
+          <t>102683612.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.30</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>45.74</v>
+        <v>54.96</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>25湘江资产MTN001</t>
+          <t>24滨建投MTN010</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>1.54Y+2.00Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.6250</t>
+          <t>1.8349</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8400/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>长沙湘江资产管理有限公司</t>
+          <t>天津滨海新区建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C+ 33.38</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7747,19 +7739,19 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.52</v>
+        <v>4.52</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.81%~1.91%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7770,17 +7762,17 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>天津市-滨海新区</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额为4亿元,募集资金拟全部用于偿还发行人存量有息债务。</t>
+          <t>本次中期票据注册规模90亿元，本期中期票据基础发行规模0亿元，发行金额上限5亿元【24滨建投MTN013】</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,华夏银行股份有限公司</t>
+          <t>中信银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7801,7 +7793,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>长沙湘江资产管理有限公司2026年度第一期中期票据</t>
+          <t>天津滨海新区建设投资集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7811,14 +7803,10 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK33" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-14</t>
+        </is>
+      </c>
+      <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
@@ -7836,32 +7824,32 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>资产管理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7890,23 +7878,23 @@
         </is>
       </c>
       <c r="AZ33" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26泰控01</t>
+          <t>26湘江资产MTN001</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>09-11 19:00</t>
+          <t>09-11 18:00</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>520478.SZ</t>
+          <t>102683611.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -7915,40 +7903,40 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.7</v>
+        <v>4.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.7</v>
+        <v>4.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.70 ~ 2.30</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>132.74</v>
+        <v>45.74</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>25泰金01</t>
+          <t>25湘江资产MTN001</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>1.53Y</t>
+          <t>1.54Y+2.00Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2.0172</t>
+          <t>1.6250</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7958,12 +7946,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>泰安金融控股集团有限公司</t>
+          <t>长沙湘江资产管理有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C- 18.39</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7973,7 +7961,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-11 15:00</t>
+          <t>09-11 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7983,133 +7971,135 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>1.81%~1.91%</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>湖南省-长沙市</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>本期债务融资工具发行金额为4亿元,募集资金拟全部用于偿还发行人存量有息债务。</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>兴业银行股份有限公司,华夏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD34" s="3"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>长沙湘江资产管理有限公司2026年度第一期中期票据</t>
+        </is>
+      </c>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK34" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="U34" s="4" t="n">
-        <v>1.1754</v>
-      </c>
-      <c r="V34" s="3"/>
-      <c r="W34" s="3" t="inlineStr">
-        <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="AA34" s="3" t="inlineStr">
-        <is>
-          <t>山东省-泰安市</t>
-        </is>
-      </c>
-      <c r="AB34" s="3" t="inlineStr">
-        <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于偿还回售公司债券。[23泰金01]</t>
-        </is>
-      </c>
-      <c r="AC34" s="3" t="inlineStr">
-        <is>
-          <t>东兴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD34" s="3" t="inlineStr">
-        <is>
-          <t>泰安岳峰投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="AE34" s="3" t="inlineStr">
-        <is>
-          <t>公司债券</t>
-        </is>
-      </c>
-      <c r="AF34" s="3" t="inlineStr">
-        <is>
-          <t>地方国有企业</t>
-        </is>
-      </c>
-      <c r="AG34" s="3" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="AH34" s="3" t="inlineStr">
-        <is>
-          <t>泰安金融控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
-        </is>
-      </c>
-      <c r="AI34" s="3" t="inlineStr">
-        <is>
-          <t>私募</t>
-        </is>
-      </c>
-      <c r="AJ34" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-15</t>
-        </is>
-      </c>
-      <c r="AK34" s="3"/>
-      <c r="AL34" s="3" t="inlineStr">
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>资产管理</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>资产管理</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="AO34" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ34" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR34" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>金融控股</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV34" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW34" s="3" t="inlineStr">
@@ -8127,12 +8117,14 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ34" s="3"/>
+      <c r="AZ34" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26延长K8</t>
+          <t>26泰控01</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -8142,7 +8134,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>246076.SH</t>
+          <t>520478.SZ</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -8151,55 +8143,55 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>45.0</v>
+        <v>5.7</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>45.0</v>
+        <v>5.7</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.00</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.55</v>
+        <v>2.75</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>12.74</v>
+        <v>132.74</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26延长K7</t>
+          <t>25泰金01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>1.53Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.7218</t>
+          <t>2.0172</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1.7100/1.6900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>陕西延长石油(集团)有限责任公司</t>
+          <t>泰安金融控股集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>B 51.28</t>
+          <t>C- 18.39</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8219,45 +8211,49 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>2.7711</v>
+        <v>1.1754</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t>1.64%~1.74%</t>
-        </is>
-      </c>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X35" s="3"/>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z35" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>陕西省-延安市</t>
+          <t>山东省-泰安市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过45亿元,募集资金扣除发行费用后,拟用于偿还有息债务和补充流动资金;其中30亿元拟用于偿还有息债务,剩余15亿元拟用于补充日常经营流动资金</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于偿还回售公司债券。[23泰金01]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,国投证券股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,中信证券股份有限公司,招商证券股份有限公司,申万宏源证券有限公司,东吴证券股份有限公司,中国银河证券股份有限公司,广发证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD35" s="3"/>
+          <t>东兴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr">
+        <is>
+          <t>泰安岳峰投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE35" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -8270,29 +8266,25 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>陕西延长石油(集团)有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第八期)</t>
+          <t>泰安金融控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK35" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
           <t/>
@@ -8300,42 +8292,42 @@
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>其他石油石化</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>石油开采</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8345,7 +8337,7 @@
       </c>
       <c r="AV35" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW35" s="3" t="inlineStr">
@@ -8368,7 +8360,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26肥西03</t>
+          <t>26延长K8</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8378,64 +8370,64 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>283285.SH</t>
+          <t>246076.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>2.6</v>
+        <v>45.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2.6</v>
+        <v>45.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.30 ~ 2.00</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>50.96</v>
+        <v>12.74</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26肥西02</t>
+          <t>26延长K7</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.79Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.7284</t>
+          <t>1.7218</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/1.6900</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>肥西县产城国创控股集团有限公司</t>
+          <t>陕西延长石油(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 17.70</t>
+          <t>B 51.28</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8445,7 +8437,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-11 16:00</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8455,16 +8447,16 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>2.31</v>
+        <v>2.7711</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
@@ -8480,17 +8472,17 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>陕西省-延安市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过2.60亿元(含2.60亿元),募集资金扣除发行费用后拟全部用于偿还公司债券兑付或回售本金[23产控03]</t>
+          <t>本期债券发行规模为不超过45亿元,募集资金扣除发行费用后,拟用于偿还有息债务和补充流动资金;其中30亿元拟用于偿还有息债务,剩余15亿元拟用于补充日常经营流动资金</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,财达证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,国投证券股份有限公司,中国国际金融股份有限公司,东方证券股份有限公司,中信证券股份有限公司,招商证券股份有限公司,申万宏源证券有限公司,东吴证券股份有限公司,中国银河证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
@@ -8511,22 +8503,22 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>肥西县产城国创控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>陕西延长石油(集团)有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第八期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
+          <t>2031-09-14</t>
         </is>
       </c>
       <c r="AK36" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL36" s="3" t="inlineStr">
@@ -8536,42 +8528,42 @@
       </c>
       <c r="AM36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他石油石化</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>石油开采</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8604,7 +8596,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26合滨02</t>
+          <t>26肥西03</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8614,7 +8606,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>283886.SH</t>
+          <t>283285.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -8623,40 +8615,40 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2.0</v>
+        <v>2.6</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2.0</v>
+        <v>2.6</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>48.96</v>
+        <v>50.96</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26合滨01</t>
+          <t>26肥西02</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>2.50Y</t>
+          <t>2.79Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.7181</t>
+          <t>1.7284</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8666,12 +8658,12 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>合肥市滨湖新区建设投资有限公司</t>
+          <t>肥西县产城国创控股集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>B- 43.61</t>
+          <t>C- 17.70</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8691,26 +8683,26 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>5.7</v>
+        <v>2.31</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
@@ -8721,12 +8713,12 @@
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过2亿元(含2亿元)，拟全部用于偿还回售的公司债券本金[23合滨02]</t>
+          <t>本期债券发行总额不超过2.60亿元(含2.60亿元),募集资金扣除发行费用后拟全部用于偿还公司债券兑付或回售本金[23产控03]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>中信建投证券股份有限公司,财达证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8747,7 +8739,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>合肥市滨湖新区建设投资有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>肥西县产城国创控股集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8757,13 +8749,17 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
-        </is>
-      </c>
-      <c r="AK37" s="3"/>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK37" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t/>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
@@ -8773,17 +8769,17 @@
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>5*无效</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
@@ -8836,70 +8832,74 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26国元证券CP011</t>
+          <t>26合滨02</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>09-11 17:00</t>
+          <t>09-11 19:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>072610184.IB</t>
+          <t>283886.SH</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="G38" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
       <c r="H38" s="4" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>32.25</v>
+        <v>48.96</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26国元证券CP007</t>
+          <t>26合滨01</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>244D</t>
+          <t>2.50Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.5033</t>
+          <t>1.7181</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.5600/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>国元证券股份有限公司</t>
+          <t>合肥市滨湖新区建设投资有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C 29.22</t>
+          <t>B- 43.61</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-11 09:00</t>
+          <t>09-11 16:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8922,21 +8922,23 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U38" s="3"/>
+      <c r="U38" s="4" t="n">
+        <v>5.7</v>
+      </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
@@ -8945,16 +8947,20 @@
           <t>安徽省-合肥市</t>
         </is>
       </c>
-      <c r="AB38" s="3"/>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>本期债券发行金额为不超过2亿元(含2亿元)，拟全部用于偿还回售的公司债券本金[23合滨02]</t>
+        </is>
+      </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>国元证券股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8964,68 +8970,68 @@
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>国元证券股份有限公司2026年度第十一期短期融资券</t>
+          <t>合肥市滨湖新区建设投资有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2027-06-11</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5*无效</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9058,74 +9064,70 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26中化股SCP011</t>
+          <t>26国元证券CP011</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
+          <t>09-11 17:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>012682237.IB</t>
+          <t>072610184.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>0.08Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>1.27 ~ 1.47</t>
-        </is>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="G39" s="3"/>
       <c r="H39" s="4" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>16.3</v>
+        <v>32.25</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>21中化04</t>
+          <t>26国元证券CP007</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>79D</t>
+          <t>244D</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.4992</t>
+          <t>1.5033</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/1.4400</t>
+          <t>1.5600/1.5000</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司</t>
+          <t>国元证券股份有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>A- 64.37</t>
+          <t>C 29.22</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9135,7 +9137,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-11 11:00</t>
+          <t>09-11 09:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -9148,18 +9150,16 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="U39" s="4" t="n">
-        <v>1.145</v>
-      </c>
+      <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
@@ -9170,28 +9170,24 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="AB39" s="3" t="inlineStr">
-        <is>
-          <t>发行人本期超短期融资券的发行规模为20亿元,募集资金将用于补充流动资金及偿还有息债务。</t>
-        </is>
-      </c>
+          <t>安徽省-合肥市</t>
+        </is>
+      </c>
+      <c r="AB39" s="3"/>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,广发银行股份有限公司</t>
+          <t>国元证券股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG39" s="3" t="inlineStr">
@@ -9201,7 +9197,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司2026年度第十一期超短期融资券</t>
+          <t>国元证券股份有限公司2026年度第十一期短期融资券</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9211,7 +9207,7 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2027-06-11</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
@@ -9222,7 +9218,7 @@
       </c>
       <c r="AM39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AN39" s="3" t="inlineStr">
@@ -9232,32 +9228,32 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>石油化工与贸易</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>石油开采</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9285,81 +9281,79 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ39" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ39" s="3"/>
     </row>
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26豫通Y6</t>
+          <t>26中化股SCP011</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>09-11 19:00</t>
+          <t>09-11 18:00</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>246049.SH</t>
+          <t>012682237.IB</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>0.08Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.27 ~ 1.47</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>37.74</v>
+        <v>16.3</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26豫通Y4</t>
+          <t>21中化04</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.82Y+N</t>
+          <t>79D</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.8604</t>
+          <t>1.4992</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>河南交通投资集团有限公司</t>
+          <t>中国中化股份有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C 25.36</t>
+          <t>A- 64.37</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9369,7 +9363,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-11 16:00</t>
+          <t>09-11 11:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -9383,17 +9377,17 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>4.91</v>
+        <v>1.145</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.43%~1.47%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
@@ -9401,45 +9395,41 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z40" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>河南省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过15.00亿元，募集资金扣除发行费用后，其中9.00亿元拟用于偿还到期公司债券，其余拟根据发行人的财务状况和资金需求情况用于生产性支出，包括偿还到期债务、补充流动资金、项目建设及运营、股权投资（含基金出资）等</t>
+          <t>发行人本期超短期融资券的发行规模为20亿元,募集资金将用于补充流动资金及偿还有息债务。</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,东方证券股份有限公司,国开证券股份有限公司</t>
+          <t>兴业银行股份有限公司,广发银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>河南交通投资集团有限公司2026年面向专业投资者公开发行可续期公司债券(第五期)</t>
+          <t>中国中化股份有限公司2026年度第十一期超短期融资券</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9449,17 +9439,13 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK40" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
@@ -9474,32 +9460,32 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>石油化工与贸易</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>石油开采</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9514,7 +9500,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -9527,12 +9513,14 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ40" s="3"/>
+      <c r="AZ40" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26黔源GCKV01</t>
+          <t>26豫通Y6</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9542,88 +9530,100 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>525003.SZ</t>
+          <t>246049.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>35.74</v>
+        <v>37.74</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>26豫通Y4</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>4.82Y+N</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>1.8604</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>河南交通投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>C 25.36</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>09-11 16:00</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>贵州黔源电力股份有限公司</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>09-11 14:00</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>2.7</v>
+        <v>4.91</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X41" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>1.82%~1.92%</t>
+        </is>
+      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -9636,17 +9636,17 @@
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>河南省</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司绿色项目贷款。</t>
+          <t>本期债券募集资金不超过15.00亿元，募集资金扣除发行费用后，其中9.00亿元拟用于偿还到期公司债券，其余拟根据发行人的财务状况和资金需求情况用于生产性支出，包括偿还到期债务、补充流动资金、项目建设及运营、股权投资（含基金出资）等</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>川财证券有限责任公司,中信建投证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,中信建投证券股份有限公司,东方证券股份有限公司,国开证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9657,17 +9657,17 @@
       </c>
       <c r="AF41" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>贵州黔源电力股份有限公司2026年面向专业投资者公开发行碳中和绿色科技创新乡村振兴公司债券(第一期)(生物多样性挂钩)(支持生态文明建设先行区)</t>
+          <t>河南交通投资集团有限公司2026年面向专业投资者公开发行可续期公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9687,50 +9687,54 @@
       </c>
       <c r="AL41" s="3" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>高速</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>高速公路</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO41" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP41" s="3"/>
-      <c r="AQ41" s="3" t="inlineStr">
-        <is>
-          <t>公用事业</t>
-        </is>
-      </c>
-      <c r="AR41" s="3" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="AS41" s="3" t="inlineStr">
-        <is>
-          <t>水电</t>
-        </is>
-      </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>电力</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV41" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9738,7 +9742,7 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
@@ -9756,7 +9760,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26沣西04</t>
+          <t>26黔源GCKV01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9766,64 +9770,56 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>284010.SH</t>
+          <t>525003.SZ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>8.5</v>
+        <v>4.0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>8.5</v>
+        <v>4.0</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.30</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>2.54</v>
+        <v>1.78</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>111.74</v>
+        <v>35.74</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr">
-        <is>
-          <t>26沣西03</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
-        <is>
-          <t>2.82Y+2.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2.7483</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/2.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>陕西西咸新区沣西发展集团有限公司</t>
+          <t>贵州黔源电力股份有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>B- 39.67</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9833,7 +9829,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-11 15:00</t>
+          <t>09-11 14:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9847,41 +9843,41 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>2.2353</v>
+        <v>2.7</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X42" s="3"/>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z42" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>贵州省-贵阳市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,拟全部用于偿还或置换区域内到期的公司债券本金</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还公司绿色项目贷款。</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>西部证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD42" s="3" t="inlineStr">
-        <is>
-          <t>西安财金投资管理有限公司</t>
-        </is>
-      </c>
+          <t>川财证券有限责任公司,中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -9889,22 +9885,22 @@
       </c>
       <c r="AF42" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>陕西西咸新区沣西发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>贵州黔源电力股份有限公司2026年面向专业投资者公开发行碳中和绿色科技创新乡村振兴公司债券(第一期)(生物多样性挂钩)(支持生态文明建设先行区)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
@@ -9919,7 +9915,7 @@
       </c>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t/>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
@@ -9934,47 +9930,43 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP42" s="3"/>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t/>
         </is>
       </c>
       <c r="AV42" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW42" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX42" s="3" t="inlineStr">
@@ -9992,74 +9984,74 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26华电江苏SCP012</t>
+          <t>26沣西04</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
+          <t>09-11 19:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>012682238.IB</t>
+          <t>284010.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>0.18Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>10.0</v>
+        <v>8.5</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>10.0</v>
+        <v>8.5</v>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 1.65</t>
+          <t>2.00 ~ 3.30</t>
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1.38</v>
+        <v>2.54</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>20.72</v>
+        <v>111.74</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26华电江苏SCP010</t>
+          <t>26沣西03</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>67D</t>
+          <t>2.82Y+2.00Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.5000</t>
+          <t>2.7483</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>1.5300/--</t>
+          <t>--/2.5000</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>华电江苏能源有限公司</t>
+          <t>陕西西咸新区沣西发展集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C 28.38</t>
+          <t>B- 39.67</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -10069,7 +10061,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>09-11 09:00</t>
+          <t>09-11 15:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -10083,82 +10075,84 @@
         </is>
       </c>
       <c r="U43" s="4" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="V43" s="4" t="n">
-        <v>1.04</v>
-      </c>
+        <v>2.2353</v>
+      </c>
+      <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t>1.45%~1.49%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X43" s="3"/>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额10亿元,募集资金全部用于归还发行人到期债务</t>
+          <t>本次公司债券募集资金扣除发行费用后,拟全部用于偿还或置换区域内到期的公司债券本金</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD43" s="3"/>
+          <t>西部证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr">
+        <is>
+          <t>西安财金投资管理有限公司</t>
+        </is>
+      </c>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>华电江苏能源有限公司2026年度第十二期超短期融资券</t>
+          <t>陕西西咸新区沣西发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
-        </is>
-      </c>
-      <c r="AK43" s="3"/>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK43" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AM43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AN43" s="3" t="inlineStr">
@@ -10168,47 +10162,47 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AV43" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
@@ -10226,7 +10220,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26中化股SCP009</t>
+          <t>26华电江苏SCP012</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -10236,64 +10230,64 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>012682235.IB</t>
+          <t>012682238.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>0.08Y</t>
+          <t>0.18Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.27 ~ 1.47</t>
+          <t>1.25 ~ 1.65</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>16.3</v>
+        <v>20.72</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>21中化04</t>
+          <t>26华电江苏SCP010</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>79D</t>
+          <t>67D</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.4992</t>
+          <t>1.5000</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/1.4400</t>
+          <t>1.5300/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司</t>
+          <t>华电江苏能源有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>A- 64.37</t>
+          <t>C 28.38</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10317,19 +10311,19 @@
         </is>
       </c>
       <c r="U44" s="4" t="n">
-        <v>1.145</v>
+        <v>3.71</v>
       </c>
       <c r="V44" s="4" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.43%~1.47%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -10340,17 +10334,17 @@
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券的发行规模为20亿元,募集资金将用于补充流动资金及偿还有息债务。</t>
+          <t>本期超短期融资券发行金额10亿元,募集资金全部用于归还发行人到期债务</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,北京银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
@@ -10371,7 +10365,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司2026年度第九期超短期融资券</t>
+          <t>华电江苏能源有限公司2026年度第十二期超短期融资券</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10381,7 +10375,7 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
@@ -10407,27 +10401,27 @@
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>石油石化</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>石油化工与贸易</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>石油开采</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10455,14 +10449,12 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ44" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ44" s="3"/>
     </row>
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26中化股SCP008</t>
+          <t>26中化股SCP009</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -10472,7 +10464,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>012682234.IB</t>
+          <t>012682235.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -10586,7 +10578,7 @@
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>渤海银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
@@ -10607,7 +10599,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>中国中化股份有限公司2026年度第八期超短期融资券</t>
+          <t>中国中化股份有限公司2026年度第九期超短期融资券</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10691,79 +10683,81 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="AZ45" s="3"/>
+      <c r="AZ45" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26成渝客专MTN001(绿色)</t>
+          <t>26中化股SCP008</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>09-14 18:00</t>
+          <t>09-11 18:00</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>102683605.IB</t>
+          <t>012682234.IB</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.08Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.99</t>
+          <t>1.27 ~ 1.47</t>
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>23.11</v>
+        <v>16.3</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>24铁道MTN007A</t>
+          <t>21中化04</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>3.00Y</t>
+          <t>79D</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.5183</t>
+          <t>1.4992</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4400</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>成渝铁路客运专线有限责任公司</t>
+          <t>中国中化股份有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>D 5.00</t>
+          <t>A- 64.37</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10783,23 +10777,23 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U46" s="4" t="n">
-        <v>4.54</v>
+        <v>1.145</v>
       </c>
       <c r="V46" s="4" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.43%~1.47%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -10807,30 +10801,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行金额10亿元,全部用于绿色产业领域,用于偿还成渝客专项目银行借款本金</t>
+          <t>发行人本期超短期融资券的发行规模为20亿元,募集资金将用于补充流动资金及偿还有息债务。</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
@@ -10845,7 +10835,7 @@
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>成渝铁路客运专线有限责任公司2026年度第一期绿色中期票据</t>
+          <t>中国中化股份有限公司2026年度第八期超短期融资券</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10855,23 +10845,23 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO46" s="3" t="inlineStr">
@@ -10879,25 +10869,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP46" s="3"/>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>石油石化</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>石油化工与贸易</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>石油开采</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10922,7 +10916,7 @@
       </c>
       <c r="AY46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AZ46" s="3"/>
@@ -10930,17 +10924,17 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26张家城投MTN005A(取消发行)</t>
+          <t>26成渝客专MTN001(绿色)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>09-11 18:00</t>
+          <t>09-14 18:00</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>DY102683613.IB</t>
+          <t>102683605.IB</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -10949,34 +10943,40 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F47" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 1.82</t>
-        </is>
-      </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
+          <t>1.50 ~ 1.99</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>23.11</v>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26张家城投MTN003B</t>
+          <t>24铁道MTN007A</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>4.46Y</t>
+          <t>3.00Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.8056</t>
+          <t>1.5183</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>张家港市城市投资发展集团有限公司</t>
+          <t>成渝铁路客运专线有限责任公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C- 19.46</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -11011,40 +11011,48 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="V47" s="4" t="n">
+        <v>1.38</v>
+      </c>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z47" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额4亿元,拟全部用于偿还本部债务融资工具本金。[21张家城投MTN004]</t>
+          <t>发行人本期拟发行金额10亿元,全部用于绿色产业领域,用于偿还成渝客专项目银行借款本金</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -11055,7 +11063,7 @@
       </c>
       <c r="AF47" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG47" s="3" t="inlineStr">
@@ -11065,7 +11073,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>张家港市城市投资发展集团有限公司2026年度第五期中期票据(品种一)(取消发行)</t>
+          <t>成渝铁路客运专线有限责任公司2026年度第一期绿色中期票据</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -11075,82 +11083,74 @@
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK47" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-15</t>
+        </is>
+      </c>
+      <c r="AK47" s="3"/>
       <c r="AL47" s="3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AM47" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AN47" s="3" t="inlineStr">
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP47" s="3"/>
+      <c r="AQ47" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY47" s="3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AO47" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AQ47" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR47" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS47" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT47" s="3" t="inlineStr">
-        <is>
-          <t>房屋建设</t>
-        </is>
-      </c>
-      <c r="AU47" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV47" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW47" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX47" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY47" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AZ47" s="3"/>
@@ -11158,74 +11158,68 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26格力01</t>
+          <t>26张家城投MTN005A(取消发行)</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>09-11 19:00</t>
+          <t>09-11 18:00</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>525002.SZ</t>
+          <t>DY102683613.IB</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>1.0</v>
+      </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I48" s="4" t="n">
-        <v>41.96</v>
-      </c>
+          <t>1.60 ~ 1.82</t>
+        </is>
+      </c>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>24格力03</t>
+          <t>26张家城投MTN003B</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>3.04Y</t>
+          <t>4.46Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.8130</t>
+          <t>1.8056</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>1.8400/1.7800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>珠海格力集团有限公司</t>
+          <t>张家港市城市投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>C 28.87</t>
+          <t>C- 19.46</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -11235,7 +11229,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>09-11 15:00</t>
+          <t>09-11 09:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -11245,48 +11239,46 @@
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="U48" s="4" t="n">
-        <v>3.42</v>
-      </c>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行等相关费用后,拟将10亿元用于偿还有息债务</t>
+          <t>本期发行金额4亿元,拟全部用于偿还本部债务融资工具本金。[21张家城投MTN004]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,广发证券股份有限公司,中国银河证券股份有限公司</t>
+          <t>中信银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF48" s="3" t="inlineStr">
@@ -11296,12 +11288,12 @@
       </c>
       <c r="AG48" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>珠海格力集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>张家港市城市投资发展集团有限公司2026年度第五期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
@@ -11311,17 +11303,17 @@
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2029-09-15</t>
+          <t>2031-09-14</t>
         </is>
       </c>
       <c r="AK48" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL48" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM48" s="3" t="inlineStr">
@@ -11331,17 +11323,17 @@
       </c>
       <c r="AN48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
@@ -11351,17 +11343,17 @@
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>装修装饰</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
@@ -11394,7 +11386,7 @@
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26粤港03</t>
+          <t>26格力01</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -11404,7 +11396,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>246080.SH</t>
+          <t>525002.SZ</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -11420,48 +11412,48 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>34.96</v>
+        <v>41.96</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>26粤港02</t>
+          <t>24格力03</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>3.04Y</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>1.6442</t>
+          <t>1.8130</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>--/1.6200</t>
+          <t>1.8400/1.7800</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>广州港股份有限公司</t>
+          <t>珠海格力集团有限公司</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>C- 12.80</t>
+          <t>C 28.87</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11485,15 +11477,19 @@
         </is>
       </c>
       <c r="U49" s="4" t="n">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X49" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y49" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -11502,17 +11498,17 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB49" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券发行总额为不超过10亿元,募集资金扣除发行费用后拟全部用于偿还有息债务。</t>
+          <t>本期公司债券募集资金扣除发行等相关费用后,拟将10亿元用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,广发证券股份有限公司,中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD49" s="3"/>
@@ -11528,12 +11524,12 @@
       </c>
       <c r="AG49" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>广州港股份有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>珠海格力集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -11553,12 +11549,12 @@
       </c>
       <c r="AL49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t/>
         </is>
       </c>
       <c r="AM49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AN49" s="3" t="inlineStr">
@@ -11573,27 +11569,27 @@
       </c>
       <c r="AP49" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ49" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT49" s="3" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>装修装饰</t>
         </is>
       </c>
       <c r="AU49" s="3" t="inlineStr">
@@ -11626,7 +11622,7 @@
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>26青水01</t>
+          <t>26粤港03</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -11636,7 +11632,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>283966.SH</t>
+          <t>246080.SH</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -11645,55 +11641,55 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="I50" s="4" t="n">
-        <v>54.96</v>
+        <v>34.96</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>25青水01</t>
+          <t>26粤港02</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>1.34Y+2.00Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.6901</t>
+          <t>1.6442</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6200</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>青岛水务集团有限公司</t>
+          <t>广州港股份有限公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>C- 17.59</t>
+          <t>C- 12.80</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11717,34 +11713,34 @@
         </is>
       </c>
       <c r="U50" s="4" t="n">
-        <v>5.14</v>
+        <v>3.54</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X50" s="3"/>
       <c r="Y50" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z50" s="3"/>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将3.00亿元用于偿还即将到期的超短期融资券本金,2.00亿元用于偿还即将到期的银行贷款。[青岛水务集团有限公司2026年度第二期超短期融资券]</t>
+          <t>本期公司债券发行总额为不超过10亿元,募集资金扣除发行费用后拟全部用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,华泰联合证券有限责任公司,中泰证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD50" s="3"/>
@@ -11765,12 +11761,12 @@
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>青岛水务集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>广州港股份有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ50" s="3" t="inlineStr">
@@ -11785,7 +11781,7 @@
       </c>
       <c r="AL50" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AM50" s="3" t="inlineStr">
@@ -11800,32 +11796,32 @@
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP50" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ50" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AT50" s="3" t="inlineStr">
         <is>
-          <t>水务</t>
+          <t>港口</t>
         </is>
       </c>
       <c r="AU50" s="3" t="inlineStr">
@@ -11858,7 +11854,7 @@
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26银桥01</t>
+          <t>26青水01</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -11868,19 +11864,19 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>246058.SH</t>
+          <t>283966.SH</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>8.9</v>
+        <v>5.0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>8.9</v>
+        <v>5.0</v>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
@@ -11888,95 +11884,95 @@
         </is>
       </c>
       <c r="H51" s="4" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>34.74</v>
+        <v>54.96</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>25青水01</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>1.34Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>1.6901</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>青岛水务集团有限公司</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>C- 17.59</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>09-11 15:00</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
-        <is>
-          <t>26昆山银桥MTN003</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>2.37Y</t>
-        </is>
-      </c>
-      <c r="M51" s="3" t="inlineStr">
-        <is>
-          <t>1.6772</t>
-        </is>
-      </c>
-      <c r="N51" s="3" t="inlineStr">
-        <is>
-          <t>1.7000/--</t>
-        </is>
-      </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>昆山银桥控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="inlineStr">
-        <is>
-          <t>C- 13.37</t>
-        </is>
-      </c>
-      <c r="Q51" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="R51" s="3" t="inlineStr">
-        <is>
-          <t>09-11 15:00</t>
-        </is>
-      </c>
-      <c r="S51" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
       <c r="U51" s="4" t="n">
-        <v>6.02</v>
+        <v>5.14</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X51" s="3"/>
       <c r="Y51" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不超过8.90亿元(含8.90亿元),募集资金在扣除发行费用后仅用于置换偿还25银桥01公司债券本金的自有资金。[25银桥01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将3.00亿元用于偿还即将到期的超短期融资券本金,2.00亿元用于偿还即将到期的银行贷款。[青岛水务集团有限公司2026年度第二期超短期融资券]</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,中信证券股份有限公司,华泰联合证券有限责任公司</t>
+          <t>东方证券股份有限公司,华泰联合证券有限责任公司,中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD51" s="3"/>
@@ -11997,23 +11993,27 @@
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>昆山银桥控股集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>青岛水务集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ51" s="3" t="inlineStr">
         <is>
-          <t>2031-09-15</t>
-        </is>
-      </c>
-      <c r="AK51" s="3"/>
+          <t>2029-09-15</t>
+        </is>
+      </c>
+      <c r="AK51" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t/>
         </is>
       </c>
       <c r="AM51" s="3" t="inlineStr">
@@ -12033,27 +12033,27 @@
       </c>
       <c r="AP51" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ51" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AT51" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水务</t>
         </is>
       </c>
       <c r="AU51" s="3" t="inlineStr">
